--- a/sampleprojects/TaxReturn/TaxReturn_DecisionTables.xlsx
+++ b/sampleprojects/TaxReturn/TaxReturn_DecisionTables.xlsx
@@ -19,18 +19,33 @@
     <sheet name="Calculate_Standard_Deduction" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Calculate_Itemized_Deductions" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Calculate_SALT_Deduction" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Calculate_Mortgage_Interest" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Calculate_Charitable_Deduction" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Calculate_Taxable_Income" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Calculate_Tax_Liability" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Apply_Tax_Brackets" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Calculate_Credits" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Calculate_Child_Tax_Credit" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Calculate_Final_Balance" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Calculate_EITC" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Calculate_Education_Credits" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Calculate_QBI_Deduction" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Validate_Results" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Sum_Primary_Residence_Tax" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Calculate_Mortgage_Interest" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Filter_Primary_Residence" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Calculate_Charitable_Deduction" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Filter_Charity_Deduction" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Calculate_Taxable_Income" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Calculate_Tax_Liability" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Apply_Tax_Brackets" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Apply_Tax_Brackets_MFJ" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Apply_Tax_Brackets_Single" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Calculate_Credits" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Calculate_Child_Tax_Credit" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Calculate_Final_Balance" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Calculate_EITC" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Calculate_Education_Credits" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Calculate_Education_Credit_Per_" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Calculate_QBI_Deduction" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Validate_Results" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Validate_AGI" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Validate_Taxable_Income" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Validate_Total_Tax" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Validate_Summary" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Filter_Self_Employed_Taxpayer" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Filter_Taxpayer_Vehicle" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Filter_Rental_Property" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Count_EITC_Qualifying_Child" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Calculate_Mortgage_Interest_For" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -785,34 +800,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Calculate_Mortgage_Interest</t>
+          <t>Sum_Primary_Residence_Tax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>FIRST</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Calculates mortgage interest deduction for qualified residences per Schedule A Lines 8a-8e, Publicat...</t>
+          <t>Helper table for SALT calculation. Adds property tax to running total if property is primary residen...</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Calculate_Charitable_Deduction</t>
+          <t>Calculate_Mortgage_Interest</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -822,19 +837,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Calculates charitable contribution deduction per Schedule A Lines 11-14, Publication 526, IRC Sectio...</t>
+          <t>Calculates mortgage interest deduction for qualified residences per Schedule A Lines 8a-8e, Publicat...</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Calculate_Taxable_Income</t>
+          <t>Filter_Primary_Residence</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -844,41 +859,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Calculates taxable income per Form 1040 Line 15, IRC Section 63. Subtracts deductions and QBI deduct...</t>
+          <t>Helper table that processes property if it is a primary residence.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Calculate_Tax_Liability</t>
+          <t>Calculate_Charitable_Deduction</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FIRST</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Calculates total tax liability including regular tax (using tax brackets per IRC Section 1) and self...</t>
+          <t>Calculates charitable contribution deduction per Schedule A Lines 11-14, Publication 526, IRC Sectio...</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Apply_Tax_Brackets</t>
+          <t>Filter_Charity_Deduction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,63 +903,63 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Applies marginal tax brackets to calculate regular tax per Form 1040 Line 16, IRC Section 1. Uses 20...</t>
+          <t>Helper table that processes deduction if category is charity.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Calculate_Credits</t>
+          <t>Calculate_Taxable_Income</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>FIRST</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Calculates tax credits including Child Tax Credit (CTC), Other Dependent Credit (ODC), and Additiona...</t>
+          <t>Calculates taxable income per Form 1040 Line 15, IRC Section 63. Subtracts deductions and QBI deduct...</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Calculate_Child_Tax_Credit</t>
+          <t>Calculate_Tax_Liability</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>FIRST</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Calculates Child Tax Credit (CTC) and Other Dependent Credit (ODC) per Schedule 8812, Publication 97...</t>
+          <t>Calculates total tax liability including regular tax (using tax brackets per IRC Section 1) and self...</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Calculate_Final_Balance</t>
+          <t>Apply_Tax_Brackets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -954,19 +969,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Calculates final tax balance - total tax minus credits and payments to determine refund or amount ow...</t>
+          <t>Applies marginal tax brackets to calculate regular tax per Form 1040 Line 16, IRC Section 1. Uses 20...</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Calculate_EITC</t>
+          <t>Apply_Tax_Brackets_MFJ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -976,73 +991,403 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Calculates Earned Income Tax Credit per Schedule EIC, Publication 596, IRC 32. EITC is a refundable ...</t>
+          <t>Calculates regular tax using MFJ brackets. Each column represents a bracket range.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Calculate_Education_Credits</t>
+          <t>Apply_Tax_Brackets_Single</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>FIRST</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Calculates education credits (AOTC and LLC) per Form 8863, Publication 970, IRC 25A. AOTC is up to $...</t>
+          <t>Calculates regular tax using Single brackets. Each column represents a bracket range.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Calculate_QBI_Deduction</t>
+          <t>Calculate_Credits</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FIRST</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Calculates Qualified Business Income deduction per Form 8995/8995-A, Publication 535, IRC 199A. The ...</t>
+          <t>Calculates tax credits including Child Tax Credit (CTC), Other Dependent Credit (ODC), and Additiona...</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Calculate_Child_Tax_Credit</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Calculates Child Tax Credit (CTC) and Other Dependent Credit (ODC) per Schedule 8812, Publication 97...</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Calculate_Final_Balance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Calculates final tax balance - total tax minus credits and payments to determine refund or amount ow...</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Calculate_EITC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Calculates Earned Income Tax Credit per Schedule EIC, Publication 596, IRC 32. EITC is a refundable ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Calculate_Education_Credits</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Calculates education credits (AOTC and LLC) per Form 8863, Publication 970, IRC 25A. AOTC is up to $...</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Calculate_Education_Credit_Per_Dependent</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Calculates education credit for a single dependent. Determines AOTC vs LLC eligibility and applies p...</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Calculate_QBI_Deduction</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Calculates Qualified Business Income deduction per Form 8995/8995-A, Publication 535, IRC 199A. The ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Validate_Results</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Validates calculated results against expected values from test case. Logs any discrepancies for revi...</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8100</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Validate_AGI</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Validates AGI against expected value. Sets validation_passed to false on mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8200</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Validate_Taxable_Income</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Validates taxable income against expected value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>8300</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Validate_Total_Tax</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Validates total tax against expected value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8400</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Validate_Summary</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Logs overall validation summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9010</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Filter_Self_Employed_Taxpayer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Helper table that processes taxpayer if self-employed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>9020</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Filter_Taxpayer_Vehicle</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Helper table that processes vehicle if it belongs to current taxpayer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>9030</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Filter_Rental_Property</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Helper table that processes property if it is a rental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>9040</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Count_EITC_Qualifying_Child</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Helper table that increments counter if dependent is qualifying child for EITC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>9050</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Calculate_Mortgage_Interest_For_Property</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Processes mortgage interest for a single property. Called by filter table.</t>
         </is>
       </c>
     </row>
@@ -1787,6 +2132,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Sum_Primary_Residence_Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 3215</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Helper table for SALT calculation. Adds property tax to running total if property is primary residence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>property.type equals primary_residence</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Property is primary residence</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Add property_taxes to running total</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Add property tax to total</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Not a primary residence - skip</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Skip non-primary residence</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2032,7 +2544,174 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Filter_Primary_Residence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 3221</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Helper table that processes property if it is a primary residence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>property.type equals primary_residence</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Property is primary residence</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Continue processing this property</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Process primary residence</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Not a primary residence - skip</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Skip non-primary residence</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2195,13 +2874,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2214,14 +2893,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Decision Table: Calculate_Taxable_Income</t>
+          <t>Decision Table: Filter_Charity_Deduction</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Table Number: 4000</t>
+          <t>Table Number: 3231</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2233,7 +2912,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Description: Calculates taxable income per Form 1040 Line 15, IRC Section 63. Subtracts deductions and QBI deduction from AGI.</t>
+          <t>Description: Helper table that processes deduction if category is charity.</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2958,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>result.total_se_income greater than 0</t>
+          <t>deduction.category equals charity</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Has self-employment income for QBI</t>
+          <t>Deduction is charity category</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -2313,12 +2992,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Calculate QBI deduction per IRC 199A (20% of qualified business income)</t>
+          <t>Add to itemized deductions</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Calculate QBI deduction</t>
+          <t>Process charity deduction</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -2336,76 +3015,18 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Set QBI deduction to zero</t>
+          <t>Not a charity deduction - skip</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>No QBI deduction</t>
+          <t>Skip non-charity deduction</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr"/>
       <c r="E10" s="13" t="inlineStr">
         <is>
           <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Calculate taxable income (AGI - deductions - QBI)</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Calculate taxable income</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Policy Statements</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Column 1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Taxable income calculated with QBI deduction per IRC 199A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Column 2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Taxable income calculated per Form 1040 Line 15</t>
         </is>
       </c>
     </row>
@@ -2414,418 +3035,6 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Decision Table: Calculate_Tax_Liability</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Table Number: 5000</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Type: FIRST</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Description: Calculates total tax liability including regular tax (using tax brackets per IRC Section 1) and self-employment tax (Schedule SE, IRC Section 1401). Form 1040 Lines 16-24.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Initial Actions</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Initialize tax calculation</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>"TAX CALCULATION (Form 1040 Lines 16-24)" job.audit_trail swap addto</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Col 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>CONDITIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>perform when called</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Always calculate</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>ACTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Apply_Tax_Brackets</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Calculate regular tax using brackets</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Sum SE tax from all taxpayers</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Add SE tax from all taxpayers</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Sum regular tax and SE tax</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Calculate total tax before credits</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A11:C11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Decision Table: Apply_Tax_Brackets</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Table Number: 5100</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Type: FIRST</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Description: Applies marginal tax brackets to calculate regular tax per Form 1040 Line 16, IRC Section 1. Uses 2025 estimated bracket amounts for MFJ, Single, and other filing statuses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Col 1</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Col 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>CONDITIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>filing_status equals MFJ or QSS</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Married Filing Jointly</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>otherwise</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Single or other</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>ACTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Apply MFJ tax brackets per IRC 1(a)</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Calculate MFJ tax</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Apply Single tax brackets per IRC 1(c)</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Calculate Single tax</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr"/>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Policy Statements</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Column 1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Tax calculated using MFJ brackets per IRC 1(a), Form 1040 Line 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Column 2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Tax calculated using Single brackets per IRC 1(c), Form 1040 Line 16</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2845,209 +3054,213 @@
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Decision Table: Calculate_Credits</t>
+          <t>Decision Table: Calculate_Taxable_Income</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Table Number: 6000</t>
+          <t>Table Number: 4000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Type: ALL</t>
+          <t>Type: FIRST</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Description: Calculates tax credits including Child Tax Credit (CTC), Other Dependent Credit (ODC), and Additional Child Tax Credit (ACTC) per Form 1040 Lines 19-21, Schedule 8812, IRC Section 24.</t>
+          <t>Description: Calculates taxable income per Form 1040 Line 15, IRC Section 63. Subtracts deductions and QBI deduction from AGI.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Initial Actions</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Initialize credit totals</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.0 /result.total_ctc xdef
-0.0 /result.total_odc xdef
-0.0 /result.total_actc xdef
-0.0 /result.total_credits xdef
-"CREDITS (Form 1040 Lines 19-21)" job.audit_trail swap addto</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>result.total_se_income greater than 0</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Has self-employment income for QBI</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Col 1</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>CONDITIONS</t>
-        </is>
-      </c>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Calculate QBI deduction per IRC 199A (20% of qualified business income)</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Calculate QBI deduction</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>perform when called</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Always process credits</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>*</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Set QBI deduction to zero</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>No QBI deduction</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>ACTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Calculate_Child_Tax_Credit</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Calculate child tax credits for all dependents</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Calculate taxable income (AGI - deductions - QBI), minimum zero</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Calculate taxable income (floor at zero)</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Calculate_EITC</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Calculate EITC</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Policy Statements</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Calculate_Education_Credits</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Calculate education credits</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Column 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Taxable income calculated with QBI deduction per IRC 199A</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Calculate total credits</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Sum total credits</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Column 2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Taxable income calculated per Form 1040 Line 15</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3059,298 +3272,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Decision Table: Calculate_Child_Tax_Credit</t>
+          <t>Decision Table: Calculate_Tax_Liability</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Table Number: 6100</t>
+          <t>Table Number: 5000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Type: ALL</t>
+          <t>Type: FIRST</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Description: Calculates Child Tax Credit (CTC) and Other Dependent Credit (ODC) per Schedule 8812, Publication 972, IRC Section 24. CTC requires child under 17 with SSN. ODC is $500 for dependents who dont qualify for CTC.</t>
+          <t>Description: Calculates total tax liability including regular tax (using tax brackets per IRC Section 1) and self-employment tax (Schedule SE, IRC Section 1401). Form 1040 Lines 16-24.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Initial Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Initialize tax calculation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>"TAX CALCULATION (Form 1040 Lines 16-24)" job.audit_trail swap addto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Col 1</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Col 2</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Col 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CONDITIONS</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>dependent.relationship equals child</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Is a qualifying child (relationship)</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>dependent.age less than ctc_age_limit</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Under age 17 at end of year</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>dependent.has_ssn equals true</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Has valid SSN</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>perform when called</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Always calculate</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>ACTIONS</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Award $2,000 CTC per IRC 24(a)</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Award Child Tax Credit</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr"/>
-      <c r="F11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Award $500 ODC for dependent age 17+ per IRC 24(h)(4)</t>
+          <t>Apply_Tax_Brackets</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Award Other Dependent Credit (age 17)</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr"/>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr"/>
+          <t>Calculate regular tax using brackets</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Sum SE tax from all taxpayers</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Add SE tax from all taxpayers</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Award $500 ODC for non-child dependent</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Non-child dependent gets ODC</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr"/>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Policy Statements</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Column 1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Child Tax Credit awarded per IRC 24(a), Schedule 8812</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Column 2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Other Dependent Credit for child age 17+ per IRC 24(h)(4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Column 3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Other Dependent Credit for non-child dependent per IRC 24(h)(4)</t>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Sum regular tax and SE tax</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Calculate total tax before credits</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3967,7 +4072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3980,14 +4085,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Decision Table: Calculate_Final_Balance</t>
+          <t>Decision Table: Apply_Tax_Brackets</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Table Number: 7000</t>
+          <t>Table Number: 5100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3999,7 +4104,1043 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Description: Calculates final tax balance - total tax minus credits and payments to determine refund or amount owed per Form 1040 Lines 33-37.</t>
+          <t>Description: Applies marginal tax brackets to calculate regular tax per Form 1040 Line 16, IRC Section 1. Uses 2025 estimated bracket amounts for MFJ, Single, and other filing statuses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>filing_status equals MFJ or QSS</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Married Filing Jointly</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>otherwise</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Single or other</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Apply MFJ tax brackets per IRC 1(a)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Calculate MFJ tax</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Apply Single tax brackets per IRC 1(c)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Calculate Single tax</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr"/>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Policy Statements</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Column 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tax calculated using MFJ brackets per IRC 1(a), Form 1040 Line 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Column 2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tax calculated using Single brackets per IRC 1(c), Form 1040 Line 16</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Apply_Tax_Brackets_MFJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 5110</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Calculates regular tax using MFJ brackets. Each column represents a bracket range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Col 3</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Col 4</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Col 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>taxable_income at or below bracket_1_mfj</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>In bracket 1 only</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>taxable_income at or below bracket_2_mfj</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>In bracket 2</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>taxable_income at or below bracket_3_mfj</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>In bracket 3</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>taxable_income at or below bracket_4_mfj</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>In bracket 4</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Income taxed at bracket_1_rate only</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 1 tax</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr"/>
+      <c r="F12" s="13" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Full bracket 1 + partial bracket 2</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 2 tax</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr"/>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Full brackets 1-2 + partial bracket 3</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 3 tax</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr"/>
+      <c r="E14" s="13" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Full brackets 1-3 + partial bracket 4</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 4 tax</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr"/>
+      <c r="E15" s="13" t="inlineStr"/>
+      <c r="F15" s="13" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Full brackets 1-4 + partial bracket 5</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 5 tax</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Apply_Tax_Brackets_Single</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 5120</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Calculates regular tax using Single brackets. Each column represents a bracket range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Col 3</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Col 4</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Col 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>taxable_income at or below bracket_1_single</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>In bracket 1 only</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>taxable_income at or below bracket_2_single</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>In bracket 2</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>taxable_income at or below bracket_3_single</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>In bracket 3</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>taxable_income at or below bracket_4_single</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>In bracket 4</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Income taxed at bracket_1_rate only</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 1 tax</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr"/>
+      <c r="F12" s="13" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Full bracket 1 + partial bracket 2</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 2 tax</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr"/>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Full brackets 1-2 + partial bracket 3</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 3 tax</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr"/>
+      <c r="E14" s="13" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Full brackets 1-3 + partial bracket 4</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 4 tax</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr"/>
+      <c r="E15" s="13" t="inlineStr"/>
+      <c r="F15" s="13" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Full brackets 1-4 + partial bracket 5</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Bracket 5 tax</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Calculate_Credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 6000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Calculates tax credits including Child Tax Credit (CTC), Other Dependent Credit (ODC), and Additional Child Tax Credit (ACTC) per Form 1040 Lines 19-21, Schedule 8812, IRC Section 24.</t>
         </is>
       </c>
     </row>
@@ -4013,16 +5154,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Calculate total tax after credits</t>
+          <t>Initialize credit totals</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"FINAL CALCULATION (Form 1040 Lines 33-37)" job.audit_trail swap addto
-result.total_tax_before_credits result.total_credits f- /result.total_tax xdef
-{ 0.0 /result.total_tax xdef } result.total_tax 0 &lt; if
-"  Line 24 - Total Tax: $" result.total_tax cvs strconcat job.audit_trail swap addto
-"  Line 33 - Total Payments: $" result.total_payments cvs strconcat job.audit_trail swap addto</t>
+          <t>0.0 /result.total_ctc xdef
+0.0 /result.total_odc xdef
+0.0 /result.total_actc xdef
+0.0 /result.total_credits xdef
+"CREDITS (Form 1040 Lines 19-21)" job.audit_trail swap addto</t>
         </is>
       </c>
     </row>
@@ -4047,11 +5188,6 @@
           <t>Col 1</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Col 2</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -4068,22 +5204,17 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>result.total_payments greater than result.total_tax</t>
+          <t>perform when called</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Payments exceed tax (refund)</t>
+          <t>Always process credits</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -4102,12 +5233,12 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Calculate refund amount (Line 34)</t>
+          <t>Calculate_Child_Tax_Credit</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Calculate refund</t>
+          <t>Calculate child tax credits for all dependents</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -4115,7 +5246,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -4125,49 +5255,61 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Calculate amount owed (Line 37)</t>
+          <t>Calculate_EITC</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Calculate amount owed</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr">
+          <t>Calculate EITC</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Calculate_Education_Credits</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Calculate education credits</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Policy Statements</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Column 1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Taxpayer due refund per Form 1040 Line 34</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Column 2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Taxpayer owes additional tax per Form 1040 Line 37</t>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Calculate total credits</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Sum total credits</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -4182,7 +5324,310 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Calculate_Child_Tax_Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 6100</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Calculates Child Tax Credit (CTC) and Other Dependent Credit (ODC) per Schedule 8812, Publication 972, IRC Section 24. CTC requires child under 17 with SSN. ODC is $500 for dependents who dont qualify for CTC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Col 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>dependent.relationship equals child</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Is a qualifying child (relationship)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>dependent.age less than ctc_age_limit</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Under age 17 at end of year</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>dependent.has_ssn equals true</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Has valid SSN</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Award $2,000 CTC per IRC 24(a)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Award Child Tax Credit</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Award $500 ODC for dependent age 17+ per IRC 24(h)(4)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Award Other Dependent Credit (age 17)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr"/>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Award $500 ODC for non-child dependent</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Non-child dependent gets ODC</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr"/>
+      <c r="E13" s="13" t="inlineStr"/>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Policy Statements</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Column 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Child Tax Credit awarded per IRC 24(a), Schedule 8812</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Column 2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other Dependent Credit for child age 17+ per IRC 24(h)(4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Column 3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other Dependent Credit for non-child dependent per IRC 24(h)(4)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4197,21 +5642,19 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Decision Table: Calculate_EITC</t>
+          <t>Decision Table: Calculate_Final_Balance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Table Number: 6200</t>
+          <t>Table Number: 7000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4223,7 +5666,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Description: Calculates Earned Income Tax Credit per Schedule EIC, Publication 596, IRC 32. EITC is a refundable credit for low-to-moderate income workers.</t>
+          <t>Description: Calculates final tax balance - total tax minus credits and payments to determine refund or amount owed per Form 1040 Lines 33-37.</t>
         </is>
       </c>
     </row>
@@ -4237,13 +5680,354 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Calculate total tax after credits</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>"FINAL CALCULATION (Form 1040 Lines 33-37)" job.audit_trail swap addto
+result.total_tax_before_credits result.total_credits f- /result.total_tax xdef</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Col 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>result.total_tax less than 0</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Total tax is negative (floor at zero)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>result.total_payments greater than result.total_tax</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Payments exceed tax (refund)</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Set total tax to zero when negative (credits exceed tax)</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Floor total tax at zero</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr"/>
+      <c r="F13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Log tax summary to audit trail</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Log total tax and payments</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Calculate refund amount (Line 34)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Calculate refund</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Calculate amount owed (Line 37)</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Calculate amount owed</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Policy Statements</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Column 1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Credits exceed tax - total tax floored at zero, refund due</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Column 2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Taxpayer due refund per Form 1040 Line 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Column 3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Taxpayer owes additional tax per Form 1040 Line 37</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Calculate_EITC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 6200</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Calculates Earned Income Tax Credit per Schedule EIC, Publication 596, IRC 32. EITC is a refundable credit for low-to-moderate income workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Initial Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Count qualifying children for EITC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>0 allocate
-{ { 0 local@ 1 + 0 local! } dependent.relationship "child" streq dependent.age 19 &lt; and if } job.dependents forall
+{ Count_EITC_Qualifying_Child performaliased } job.dependents forall
 0 local@ /result.eitc_qualifying_children xdef
 deallocate pop</t>
         </is>
@@ -4290,6 +6074,26 @@
           <t>Col 5</t>
         </is>
       </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Col 6</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Col 7</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Col 8</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Col 9</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -4336,6 +6140,26 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
@@ -4348,12 +6172,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>AGI less than EITC income limit</t>
+          <t>EITC qualifying children 3 or more</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>AGI within limits</t>
+          <t>3+ qualifying children</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -4368,15 +6192,39 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -4386,23 +6234,59 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>EITC qualifying children count</t>
+          <t>EITC qualifying children equals 2</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Number of qualifying children</t>
+          <t>2 qualifying children</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="10" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -4412,23 +6296,59 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>EITC qualifying children equals 2</t>
+          <t>EITC qualifying children equals 1</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>2 qualifying children</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
+          <t>1 qualifying child</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr"/>
-      <c r="H13" s="10" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -4438,23 +6358,59 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>EITC qualifying children equals 1</t>
+          <t>EITC qualifying children equals 0</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>1 qualifying child</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
+          <t>0 qualifying children</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -4464,156 +6420,518 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>EITC qualifying children equals 0</t>
+          <t>AGI at or below threshold for 3+ children</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>No qualifying children</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="10" t="inlineStr"/>
+          <t>AGI below phase-out threshold (3+ children)</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>AGI at or below threshold for 2 children</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>AGI below phase-out threshold (2 children)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>AGI at or below threshold for 1 child</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>AGI below phase-out threshold (1 child)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>AGI at or below threshold for 0 children</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>AGI below phase-out threshold (0 children)</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>ACTIONS</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Calculate EITC for 3+ qualifying children per IRC 32</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Calculate EITC with 3+ children</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr"/>
-      <c r="F17" s="13" t="inlineStr"/>
-      <c r="G17" s="13" t="inlineStr"/>
-      <c r="H17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Calculate EITC for 2 qualifying children per IRC 32</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Calculate EITC with 2 children</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="13" t="inlineStr"/>
-      <c r="H18" s="13" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Calculate EITC for 1 qualifying child per IRC 32</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Calculate EITC with 1 child</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr"/>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr"/>
-      <c r="H19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Calculate EITC for 0 qualifying children per IRC 32</t>
+          <t>Maximum EITC for 3+ qualifying children per IRC 32</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Calculate EITC with no children</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr"/>
+          <t>EITC 3+ children - full amount</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="E20" s="13" t="inlineStr"/>
       <c r="F20" s="13" t="inlineStr"/>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="G20" s="13" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr"/>
+      <c r="J20" s="13" t="inlineStr"/>
+      <c r="K20" s="13" t="inlineStr"/>
+      <c r="L20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>No EITC due to no earned income</t>
+          <t>EITC for 3+ children with phase-out per IRC 32</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>No EITC - no earned income</t>
+          <t>EITC 3+ children - phase-out</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr"/>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F21" s="13" t="inlineStr"/>
       <c r="G21" s="13" t="inlineStr"/>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr"/>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="13" t="inlineStr"/>
+      <c r="K21" s="13" t="inlineStr"/>
+      <c r="L21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Maximum EITC for 2 qualifying children per IRC 32</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>EITC 2 children - full amount</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
+      <c r="E22" s="13" t="inlineStr"/>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr"/>
+      <c r="K22" s="13" t="inlineStr"/>
+      <c r="L22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>EITC for 2 children with phase-out per IRC 32</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>EITC 2 children - phase-out</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr"/>
+      <c r="E23" s="13" t="inlineStr"/>
+      <c r="F23" s="13" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr"/>
+      <c r="K23" s="13" t="inlineStr"/>
+      <c r="L23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Maximum EITC for 1 qualifying child per IRC 32</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>EITC 1 child - full amount</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr"/>
+      <c r="E24" s="13" t="inlineStr"/>
+      <c r="F24" s="13" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr"/>
+      <c r="K24" s="13" t="inlineStr"/>
+      <c r="L24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>EITC for 1 child with phase-out per IRC 32</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>EITC 1 child - phase-out</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr"/>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="13" t="inlineStr"/>
+      <c r="G25" s="13" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr"/>
+      <c r="K25" s="13" t="inlineStr"/>
+      <c r="L25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Maximum EITC for 0 qualifying children per IRC 32</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>EITC 0 children - full amount</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr"/>
+      <c r="E26" s="13" t="inlineStr"/>
+      <c r="F26" s="13" t="inlineStr"/>
+      <c r="G26" s="13" t="inlineStr"/>
+      <c r="H26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr"/>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr"/>
+      <c r="L26" s="13" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>EITC for 0 children with phase-out per IRC 32</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>EITC 0 children - phase-out</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr"/>
+      <c r="E27" s="13" t="inlineStr"/>
+      <c r="F27" s="13" t="inlineStr"/>
+      <c r="G27" s="13" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr"/>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>No EITC due to no earned income</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>No EITC - no earned income</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr"/>
+      <c r="E28" s="13" t="inlineStr"/>
+      <c r="F28" s="13" t="inlineStr"/>
+      <c r="G28" s="13" t="inlineStr"/>
+      <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr"/>
+      <c r="K28" s="13" t="inlineStr"/>
+      <c r="L28" s="13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4624,13 +6942,13 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4681,32 +6999,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Calculate education credits for all college students</t>
+          <t>Initialize education credit and process dependents</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>0.0 /result.education_credit xdef
-{
-  {
-    {
-      dependent.qualified_expenses 2000.0 fmin dependent.qualified_expenses 2000.0 f- 0.0 fmax 0.25 f* f+ aotc_max fmin /dependent.education_credit xdef
-      { dependent.education_credit aotc_phase_out_end_mfj result.agi f- aotc_phase_out_end_mfj aotc_phase_out_mfj f- fdiv f* /dependent.education_credit xdef } result.agi aotc_phase_out_mfj &gt; if
-      dependent.education_credit result.education_credit f+ /result.education_credit xdef
-      "  AOTC for " dependent.name strconcat ": $" strconcat dependent.education_credit cvs strconcat " per Form 8863, IRC 25A(i)" strconcat job.audit_trail swap addto
-    }
-    {
-      dependent.qualified_expenses 0.20 f* llc_max fmin /dependent.education_credit xdef
-      { dependent.education_credit llc_phase_out_end_mfj result.agi f- llc_phase_out_end_mfj llc_phase_out_mfj f- fdiv f* /dependent.education_credit xdef } result.agi llc_phase_out_mfj &gt; if
-      dependent.education_credit result.education_credit f+ /result.education_credit xdef
-      "  LLC for " dependent.name strconcat ": $" strconcat dependent.education_credit cvs strconcat " per Form 8863, IRC 25A(c)" strconcat job.audit_trail swap addto
-    }
-    dependent.college_year 1 &gt;= dependent.college_year 4 &lt;= and dependent.aotc_used_years 4 &lt; and result.agi aotc_phase_out_end_mfj &lt; and
-    ifelse
-  }
-  dependent.is_college_student true beq
-  if
-} job.dependents forall</t>
+{ Calculate_Education_Credit_Per_Dependent performaliased } job.dependents forall</t>
         </is>
       </c>
     </row>
@@ -4801,7 +7100,484 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Calculate_Education_Credit_Per_Dependent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 6310</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Calculates education credit for a single dependent. Determines AOTC vs LLC eligibility and applies phase-out. Called by forall loop in Calculate_Education_Credits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Col 3</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Col 4</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Col 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>dependent.is_college_student equals true</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Is college student</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>college_year 1-4 AND aotc_used_years less than 4</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Eligible for AOTC (years 1-4, not exhausted)</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>result.agi greater than aotc_phase_out_mfj</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>AGI in AOTC phase-out range</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>result.agi greater than llc_phase_out_mfj</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>AGI in LLC phase-out range</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>AOTC: 100% of first $2000 + 25% of next $2000</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Calculate AOTC (full amount)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr"/>
+      <c r="F12" s="13" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>AOTC with AGI phase-out reduction</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Calculate AOTC with phase-out</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr"/>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>LLC: 20% of qualified expenses up to $2000</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Calculate LLC (full amount)</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr"/>
+      <c r="E14" s="13" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>LLC with AGI phase-out reduction</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Calculate LLC with phase-out</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr"/>
+      <c r="E15" s="13" t="inlineStr"/>
+      <c r="F15" s="13" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Skip - dependent is not a college student</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Not a college student</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Policy Statements</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Column 1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AOTC credit (full) per Form 8863, IRC 25A(b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Column 2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AOTC credit with phase-out per Form 8863, IRC 25A(d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Column 3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LLC credit (full) per Form 8863, IRC 25A(c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Column 4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LLC credit with phase-out per Form 8863, IRC 25A(d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Column 5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>No education credit - not a college student</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4986,193 +7762,6 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:C6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Decision Table: Validate_Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Table Number: 8000</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Type: ALL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Description: Validates calculated results against expected values from test case. Logs any discrepancies for review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Initial Actions</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Initialize validation</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>"VALIDATION RESULTS" job.audit_trail swap addto
-true /result.validation_passed xdef</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Col 1</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Col 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>CONDITIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>job has expected values for validation</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Expected values exist</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>ACTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Compare calculated vs expected values</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Validate all results</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Skip validation - no expected values provided</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>No expected values</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5438,6 +8027,1696 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A11:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Validate_Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 8000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Validates calculated results against expected values from test case. Logs any discrepancies for review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Initial Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Initialize validation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>"VALIDATION RESULTS" job.audit_trail swap addto
+true /result.validation_passed xdef</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>job has expected values for validation</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Expected values exist</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Execute validation sub-tables for each field</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Run all validations</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Skip validation - no expected values provided</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>No expected values</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr"/>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Validate_AGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 8100</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Validates AGI against expected value. Sets validation_passed to false on mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>AGI difference less than or equal to 1.0</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>AGI matches expected (within tolerance)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Log AGI pass</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>AGI validation passed</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Log AGI mismatch and set validation_passed to false</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>AGI validation failed</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Validate_Taxable_Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 8200</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Validates taxable income against expected value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Taxable income difference less than or equal to 1.0</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Taxable income matches expected</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Log taxable income pass</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Taxable income validation passed</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Log taxable income mismatch</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Taxable income validation failed</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Validate_Total_Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 8300</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Validates total tax against expected value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Total tax difference less than or equal to 1.0</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Total tax matches expected</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Log total tax pass</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Total tax validation passed</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Log total tax mismatch</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Total tax validation failed</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Validate_Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 8400</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Logs overall validation summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>result.validation_passed equals true</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>All validations passed</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Log validation success</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>All tests passed</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Log validation failure</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Some tests failed</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Filter_Self_Employed_Taxpayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 9010</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Helper table that processes taxpayer if self-employed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>taxpayer.is_self_employed equals true</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Taxpayer is self-employed</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Execute self-employment processing</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Process self-employed taxpayer</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Not self-employed - skip</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Skip non-self-employed</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Filter_Taxpayer_Vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 9020</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Helper table that processes vehicle if it belongs to current taxpayer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>vehicle.taxpayer_id equals taxpayer.id</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Vehicle belongs to current taxpayer</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Vehicle belongs to taxpayer - continue processing</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Process vehicle</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Vehicle does not belong to taxpayer - skip</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Skip vehicle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Filter_Rental_Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 9030</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Helper table that processes property if it is a rental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>property.type equals rental</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Property is rental</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Property is rental - continue processing</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Process rental</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Property is not rental - skip</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Skip non-rental</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Count_EITC_Qualifying_Child</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 9040</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Helper table that increments counter if dependent is qualifying child for EITC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>relationship is child AND age under 19</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Is qualifying child</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Add 1 to qualifying children count</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Increment counter</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>No action needed</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Skip non-qualifying</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Table: Calculate_Mortgage_Interest_For_Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table Number: 9050</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type: FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Description: Processes mortgage interest for a single property. Called by filter table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>property.mortgage_interest greater than 0</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Has mortgage interest</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Add mortgage interest to itemized deductions</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Process mortgage interest</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Pop property from stack</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>No mortgage interest</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sampleprojects/TaxReturn/TaxReturn_DecisionTables.xlsx
+++ b/sampleprojects/TaxReturn/TaxReturn_DecisionTables.xlsx
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>SE net profit greater than or equal to se_threshold</t>
+          <t>SE gross income greater than or equal to se_threshold (check before expenses)</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Net SE income meets threshold for SE tax</t>
+          <t>SE gross income meets threshold for SE tax</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Calculate SE tax</t>
+          <t>Calculate SE tax if net profit exceeds threshold</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Log no SE tax required</t>
+          <t>Log no SE tax required (gross income below threshold)</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -10540,7 +10540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10548,7 +10548,6 @@
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10603,11 +10602,6 @@
           <t>Col 2</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Col 3</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -10624,12 +10618,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>property.rental_income greater than 0</t>
+          <t>property.type equals rental</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Has rental income</t>
+          <t>Is rental property</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -10638,11 +10632,6 @@
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -10656,12 +10645,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>rental net income greater than 0</t>
+          <t>property.rental_income greater than 0</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Net rental income is positive</t>
+          <t>Has rental income</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -10669,12 +10658,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -10704,12 +10688,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -10732,12 +10711,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr"/>
+      <c r="E11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -10747,12 +10721,12 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Calculate net rental income (Schedule E Line 21)</t>
+          <t>Calculate net rental income (Schedule E Line 21) and add to total</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Calculate net rental income</t>
+          <t>Calculate net rental income and add to total</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -10760,99 +10734,34 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Add net rental income to result</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Add net rental income to total</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr"/>
-      <c r="F13" s="13" t="inlineStr"/>
+      <c r="E12" s="13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Log rental loss with passive activity note</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Handle rental loss</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Policy Statements</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Column 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rental income calculated per Schedule E Part I, Publication 527, IRC 61(a)(5)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Policy Statements</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Column 1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Rental income calculated per Schedule E Part I, Publication 527, IRC 61(a)(5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Column 2</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Rental loss subject to passive activity rules per Form 8582, IRC 469</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Column 3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Property is not a rental property</t>
         </is>
@@ -10875,7 +10784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10912,138 +10821,118 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Initial Actions</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Col 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Col 2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Initialize adjustments</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.0 /result.total_adjustments xdef
-"ADJUSTMENTS TO INCOME (Schedule 1 Part II)" job.audit_trail swap addto</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>taxpayer.se_tax_deduction greater than 0</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Has SE tax to deduct</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Col 1</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Col 2</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>CONDITIONS</t>
-        </is>
-      </c>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Add deductible portion of SE tax per IRC 164(f)</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Add SE tax deduction to adjustments</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>taxpayer.se_tax_deduction greater than 0</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Has SE tax to deduct</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>ACTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Add deductible portion of SE tax per IRC 164(f)</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Add SE tax deduction to adjustments</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Log total adjustments</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Log total adjustments</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -11051,10 +10940,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
